--- a/VerveStacks_CAN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_CAN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids_kan\SubRES_Tmpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_CAN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE07FE8D-B586-4C91-BE9D-15A3FCFB7E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81AE1D46-4711-4D8A-80CF-34D1806876E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7686" uniqueCount="2234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7685" uniqueCount="2235">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -6830,6 +6830,9 @@
   </si>
   <si>
     <t>Transformer: e_w96456442-315 → e_w96456442-735</t>
+  </si>
+  <si>
+    <t>ELC,e_CA164-315,e_CA184-500,e_CA185-500,e_CA191-500,e_CA216-315,e_CA218-315,e_CA219-315,e_CA229-345,e_CA239-315,e_CA246-315,e_CA248-315,e_CA250-315,e_CA256-315,e_CA257-315,e_CA261-315,e_CA265-315,e_CA28-287,e_CA29-287,e_CA293-315,e_CA298-315,e_CA30-287,e_CA302-315,e_CA303-315,e_CA305-315,e_CA307-315,e_CA310-315,e_CA317-315,e_CA323-315,e_CA337-345,e_CA343-765,e_CA364-500,e_CA369-500,e_CA370-500,e_CA374-500,e_CA387-500,e_CA390-500,e_CA444-345,e_r10383760-500,e_r11990161-735,e_w101946689-315,e_w104084354-315,e_w104087942-315,e_w1042251776-315,e_w1066689518-315,e_w110303217-315,e_w110303217-735,e_w1116379982-345,e_w1132335692-315,e_w113855788-500,e_w117228972-345,e_w117955755-345,e_w124919871-315,e_w129284212-315,e_w129284212-735,e_w129284212-765,e_w136145755-345,e_w142578254-315,e_w156738152-500,e_w156738153-500,e_w166474302-315,e_w166475010-315,e_w166475153-315,e_w166899876-500,e_w167808338-315,e_w167860256-315,e_w168115738-315,e_w172651669-287,e_w191437318-315,e_w227671365-315,e_w232194254-315,e_w240310383-345,e_w24364552-315,e_w25495523-500,e_w25500667-500,e_w26103715-500,e_w26296871-315,e_w264390223-315,e_w272219026-345,e_w273639295-500,e_w302580598-315,e_w323564265-315,e_w32963410-500,e_w33144100-315,e_w33144100-735,e_w33728777-500,e_w34040833-315,e_w34317219-315,e_w38223686-315,e_w44138477-315,e_w44912776-315,e_w476702648-500,e_w486371739-345,e_w5065566-500,e_w511092191-315,e_w551510936-345,e_w581354518-345,e_w614612290-500,e_w637681518-735,e_w638388421-315,e_w67214412-500,e_w711797215-345,e_w72838752-315,e_w72838752-735,e_w792464552-315,e_w80575562-315,e_w805809222-315,e_w849603970-315,e_w90870078-287,e_w92544660-315,e_w94212756-315,e_w947757905-315,e_w960912589-315,e_w961152437-315,e_w961152437-735,e_w96456442-315,e_w96456442-735</t>
   </si>
 </sst>
 </file>
@@ -8704,7 +8707,7 @@
         <v>Trd_electricity import</v>
       </c>
       <c r="L18" t="s">
-        <v>19</v>
+        <v>2234</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -8724,8 +8727,9 @@
         <f>C9</f>
         <v>Trd_electricity export</v>
       </c>
-      <c r="K19" t="s">
-        <v>19</v>
+      <c r="K19" t="str">
+        <f>L18</f>
+        <v>ELC,e_CA164-315,e_CA184-500,e_CA185-500,e_CA191-500,e_CA216-315,e_CA218-315,e_CA219-315,e_CA229-345,e_CA239-315,e_CA246-315,e_CA248-315,e_CA250-315,e_CA256-315,e_CA257-315,e_CA261-315,e_CA265-315,e_CA28-287,e_CA29-287,e_CA293-315,e_CA298-315,e_CA30-287,e_CA302-315,e_CA303-315,e_CA305-315,e_CA307-315,e_CA310-315,e_CA317-315,e_CA323-315,e_CA337-345,e_CA343-765,e_CA364-500,e_CA369-500,e_CA370-500,e_CA374-500,e_CA387-500,e_CA390-500,e_CA444-345,e_r10383760-500,e_r11990161-735,e_w101946689-315,e_w104084354-315,e_w104087942-315,e_w1042251776-315,e_w1066689518-315,e_w110303217-315,e_w110303217-735,e_w1116379982-345,e_w1132335692-315,e_w113855788-500,e_w117228972-345,e_w117955755-345,e_w124919871-315,e_w129284212-315,e_w129284212-735,e_w129284212-765,e_w136145755-345,e_w142578254-315,e_w156738152-500,e_w156738153-500,e_w166474302-315,e_w166475010-315,e_w166475153-315,e_w166899876-500,e_w167808338-315,e_w167860256-315,e_w168115738-315,e_w172651669-287,e_w191437318-315,e_w227671365-315,e_w232194254-315,e_w240310383-345,e_w24364552-315,e_w25495523-500,e_w25500667-500,e_w26103715-500,e_w26296871-315,e_w264390223-315,e_w272219026-345,e_w273639295-500,e_w302580598-315,e_w323564265-315,e_w32963410-500,e_w33144100-315,e_w33144100-735,e_w33728777-500,e_w34040833-315,e_w34317219-315,e_w38223686-315,e_w44138477-315,e_w44912776-315,e_w476702648-500,e_w486371739-345,e_w5065566-500,e_w511092191-315,e_w551510936-345,e_w581354518-345,e_w614612290-500,e_w637681518-735,e_w638388421-315,e_w67214412-500,e_w711797215-345,e_w72838752-315,e_w72838752-735,e_w792464552-315,e_w80575562-315,e_w805809222-315,e_w849603970-315,e_w90870078-287,e_w92544660-315,e_w94212756-315,e_w947757905-315,e_w960912589-315,e_w961152437-315,e_w961152437-735,e_w96456442-315,e_w96456442-735</v>
       </c>
       <c r="P19">
         <v>0</v>
